--- a/data_lake/macro/South Korea/Export.xlsx
+++ b/data_lake/macro/South Korea/Export.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\South Korea\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\South Korea\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C52ABC-3D5C-4139-A6FA-3982E589AEC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A01F40A8-1FB1-4514-9964-529A921EDDE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D0939876-3207-4808-9706-D07754E61412}"/>
+    <workbookView xWindow="1536" yWindow="1464" windowWidth="21600" windowHeight="10872" xr2:uid="{D0939876-3207-4808-9706-D07754E61412}"/>
   </bookViews>
   <sheets>
     <sheet name="KOEXTOTY" sheetId="1" r:id="rId1"/>
@@ -79,12 +79,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
-    <numFmt numFmtId="168" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="[$-409]h:mm\ AM/PM;@"/>
+    <numFmt numFmtId="179" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="180" formatCode="0.0%"/>
+    <numFmt numFmtId="181" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -127,16 +127,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -160,7 +158,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -180,43 +178,43 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -539,14 +537,13 @@
   <dimension ref="A1:J790"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="12.33203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" style="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.21875" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.44140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.88671875" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.6640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.5546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.6640625" style="13" customWidth="1"/>
     <col min="9" max="9" width="11.33203125" style="8" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="9.109375" style="8"/>
   </cols>
